--- a/artfynd/A 11447-2025 artfynd.xlsx
+++ b/artfynd/A 11447-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>97652053</v>
       </c>
       <c r="B2" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650524.2281941598</v>
+        <v>650524</v>
       </c>
       <c r="R2" t="n">
-        <v>6604754.540711612</v>
+        <v>6604754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
